--- a/grupos/4BEM - Estadisticos 20222.xlsx
+++ b/grupos/4BEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="138">
   <si>
     <t>Materia</t>
   </si>
@@ -273,163 +273,163 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>PEDRO EVER</t>
+  </si>
+  <si>
+    <t>NEIL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAIR</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
+  </si>
+  <si>
+    <t>JASIEL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>CELSO ALEJANDRO</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>JUAN PABLO</t>
+  </si>
+  <si>
+    <t>DIEGO HUMBERTO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>SINAI ANTONIO</t>
+  </si>
+  <si>
+    <t>ZURIEL ELIHU</t>
+  </si>
+  <si>
+    <t>JORGE MARIO</t>
+  </si>
+  <si>
+    <t>ARIEL CHARBEL</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>DARINKA</t>
+  </si>
+  <si>
     <t>ZGAIP</t>
   </si>
   <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
     <t>OJEDA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>PEDRO EVER</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAIR</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>CELSO ALEJANDRO</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>DIEGO HUMBERTO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
-  </si>
-  <si>
-    <t>ZURIEL ELIHU</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>ARIEL CHARBEL</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>DARINKA</t>
   </si>
   <si>
     <t>YAEL</t>
@@ -934,7 +934,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -952,7 +952,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -997,7 +997,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1015,7 +1015,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1023,7 +1023,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -1041,7 +1041,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1086,7 +1086,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -1104,7 +1104,7 @@
         <v>6</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1112,7 +1112,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -1130,7 +1130,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1175,7 +1175,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1193,7 +1193,7 @@
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1201,7 +1201,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1219,7 +1219,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1264,7 +1264,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1290,7 +1290,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>9</v>
@@ -1308,7 +1308,7 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1353,7 +1353,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1371,7 +1371,7 @@
         <v>7</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1379,7 +1379,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1442,7 +1442,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1460,7 +1460,7 @@
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1468,7 +1468,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -1486,7 +1486,7 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1531,7 +1531,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1557,7 +1557,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -1575,7 +1575,7 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1620,7 +1620,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1638,7 +1638,7 @@
         <v>6</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1646,7 +1646,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>9</v>
@@ -1664,7 +1664,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1709,7 +1709,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1727,7 +1727,7 @@
         <v>5</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1735,7 +1735,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>9</v>
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1798,7 +1798,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1816,7 +1816,7 @@
         <v>5</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1824,7 +1824,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1887,7 +1887,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1905,7 +1905,7 @@
         <v>9</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1913,7 +1913,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -1931,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1976,7 +1976,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1994,7 +1994,7 @@
         <v>9</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2002,7 +2002,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -2020,7 +2020,7 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2065,7 +2065,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -2083,7 +2083,7 @@
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2091,7 +2091,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -2109,7 +2109,7 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2154,7 +2154,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -2172,7 +2172,7 @@
         <v>5</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2180,7 +2180,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -2198,7 +2198,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2243,7 +2243,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -2261,7 +2261,7 @@
         <v>6</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2269,7 +2269,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -2287,7 +2287,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2332,7 +2332,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2350,7 +2350,7 @@
         <v>5</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2358,7 +2358,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>9</v>
@@ -2376,7 +2376,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2421,7 +2421,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2439,7 +2439,7 @@
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2447,7 +2447,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>10</v>
@@ -2465,7 +2465,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2510,7 +2510,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -2528,7 +2528,7 @@
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2536,7 +2536,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>9</v>
@@ -2554,7 +2554,7 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2599,7 +2599,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2617,7 +2617,7 @@
         <v>8</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2625,7 +2625,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -2643,7 +2643,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2688,7 +2688,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2706,7 +2706,7 @@
         <v>5</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2714,7 +2714,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -2732,7 +2732,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2777,7 +2777,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2795,7 +2795,7 @@
         <v>8</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2803,7 +2803,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -2821,7 +2821,7 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2866,7 +2866,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2884,7 +2884,7 @@
         <v>7</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2892,7 +2892,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>8</v>
@@ -2910,7 +2910,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2973,7 +2973,7 @@
         <v>5</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2981,7 +2981,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C27">
         <v>10</v>
@@ -2999,7 +2999,7 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -3044,7 +3044,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -3062,7 +3062,7 @@
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3070,7 +3070,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C28">
         <v>9</v>
@@ -3088,7 +3088,7 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -3133,7 +3133,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -3151,7 +3151,7 @@
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3159,7 +3159,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3222,7 +3222,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -3240,7 +3240,7 @@
         <v>7</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3248,7 +3248,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -3266,7 +3266,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3311,7 +3311,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X30">
         <v>5</v>
@@ -3329,7 +3329,7 @@
         <v>5</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3337,7 +3337,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -3355,7 +3355,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3400,7 +3400,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3418,7 +3418,7 @@
         <v>9</v>
       </c>
       <c r="AC31">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3432,7 +3432,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3459,7 +3459,7 @@
         <v>8</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3589,7 +3589,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -3607,7 +3607,7 @@
         <v>86.7</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -3675,7 +3675,7 @@
         <v>83.3</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -3743,7 +3743,7 @@
         <v>86.7</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3793,7 +3793,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3861,7 +3861,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -3879,7 +3879,7 @@
         <v>83.3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3929,7 +3929,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C9">
         <v>70</v>
@@ -3947,7 +3947,7 @@
         <v>80</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -3997,7 +3997,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -4015,7 +4015,7 @@
         <v>83.3</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4065,7 +4065,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4083,7 +4083,7 @@
         <v>80</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4133,7 +4133,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -4151,7 +4151,7 @@
         <v>76.7</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4201,7 +4201,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>80</v>
@@ -4219,7 +4219,7 @@
         <v>76.7</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -4287,7 +4287,7 @@
         <v>83.3</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -4337,7 +4337,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -4355,7 +4355,7 @@
         <v>83.3</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -4405,7 +4405,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C16">
         <v>70</v>
@@ -4423,7 +4423,7 @@
         <v>76.7</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>70</v>
@@ -4491,7 +4491,7 @@
         <v>76.7</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -4541,7 +4541,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C18">
         <v>70</v>
@@ -4559,7 +4559,7 @@
         <v>80</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -4609,7 +4609,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C19">
         <v>70</v>
@@ -4627,7 +4627,7 @@
         <v>76.7</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -4677,7 +4677,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -4695,7 +4695,7 @@
         <v>76.7</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -4745,7 +4745,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -4763,7 +4763,7 @@
         <v>83.3</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -4831,7 +4831,7 @@
         <v>80</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -4881,7 +4881,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C23">
         <v>50</v>
@@ -4899,7 +4899,7 @@
         <v>80</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -4949,7 +4949,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -4967,7 +4967,7 @@
         <v>80</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -5017,7 +5017,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -5035,7 +5035,7 @@
         <v>80</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5085,7 +5085,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -5103,7 +5103,7 @@
         <v>76.7</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5153,7 +5153,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -5171,7 +5171,7 @@
         <v>83.3</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -5221,7 +5221,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5239,7 +5239,7 @@
         <v>83.3</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5289,7 +5289,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5307,7 +5307,7 @@
         <v>83.3</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C30">
         <v>60</v>
@@ -5375,7 +5375,7 @@
         <v>76.7</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5425,7 +5425,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -5443,7 +5443,7 @@
         <v>80</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>83.3</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -5601,86 +5601,92 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>62.07</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>37.93</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>35.71</v>
+      </c>
+      <c r="H4">
+        <v>5.9</v>
       </c>
       <c r="I4">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>62.07</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G5">
-        <v>37.93</v>
+        <v>28.57</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5691,28 +5697,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>71.43000000000001</v>
+        <v>75.86</v>
       </c>
       <c r="G6">
-        <v>28.57</v>
+        <v>24.14</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5792,7 +5798,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5827,10 +5833,10 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5841,7 +5847,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920185</v>
+        <v>21330051920186</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -5850,10 +5856,10 @@
         <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
@@ -5861,19 +5867,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920185</v>
+        <v>21330051920187</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
         <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
@@ -5881,13 +5887,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920186</v>
+        <v>21330051920188</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
         <v>110</v>
@@ -5901,19 +5907,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920186</v>
+        <v>21330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
@@ -5921,19 +5927,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920186</v>
+        <v>21330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
@@ -5941,16 +5947,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920187</v>
+        <v>21330051920191</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5961,19 +5967,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920187</v>
+        <v>21330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>54</v>
@@ -5981,19 +5987,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920187</v>
+        <v>21330051920193</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>54</v>
@@ -6001,16 +6007,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920188</v>
+        <v>19330061430023</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -6021,19 +6027,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920188</v>
+        <v>21330051920194</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>54</v>
@@ -6041,19 +6047,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920188</v>
+        <v>21330051920196</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>54</v>
@@ -6061,16 +6067,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920189</v>
+        <v>21330051920386</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -6081,19 +6087,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920189</v>
+        <v>21330051920199</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
         <v>54</v>
@@ -6101,19 +6107,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920189</v>
+        <v>21330051920201</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
         <v>54</v>
@@ -6121,16 +6127,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920190</v>
+        <v>21330051920202</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -6141,19 +6147,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920190</v>
+        <v>21330051920203</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
         <v>54</v>
@@ -6161,19 +6167,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920190</v>
+        <v>21330051920204</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>54</v>
@@ -6181,16 +6187,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920191</v>
+        <v>21330051920205</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -6201,19 +6207,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920191</v>
+        <v>21330051920206</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
         <v>54</v>
@@ -6221,19 +6227,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920191</v>
+        <v>21330051920207</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
         <v>54</v>
@@ -6241,16 +6247,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920192</v>
+        <v>21330051920208</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -6261,19 +6267,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920192</v>
+        <v>21330051920209</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
         <v>54</v>
@@ -6281,19 +6287,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920192</v>
+        <v>21330051920210</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
         <v>54</v>
@@ -6301,16 +6307,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920193</v>
+        <v>21330051920211</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -6321,19 +6327,19 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920193</v>
+        <v>21330051920212</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="E27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
         <v>54</v>
@@ -6341,19 +6347,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920193</v>
+        <v>21330051920213</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
         <v>54</v>
@@ -6361,1161 +6367,21 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330061430023</v>
+        <v>21330051920214</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330061430023</v>
-      </c>
-      <c r="B30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330061430023</v>
-      </c>
-      <c r="B31" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" t="s">
-        <v>93</v>
-      </c>
-      <c r="D31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920194</v>
-      </c>
-      <c r="B32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920194</v>
-      </c>
-      <c r="B33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920194</v>
-      </c>
-      <c r="B34" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920196</v>
-      </c>
-      <c r="B35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" t="s">
-        <v>120</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920196</v>
-      </c>
-      <c r="B36" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" t="s">
-        <v>83</v>
-      </c>
-      <c r="D36" t="s">
-        <v>120</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920196</v>
-      </c>
-      <c r="B37" t="s">
-        <v>67</v>
-      </c>
-      <c r="C37" t="s">
-        <v>83</v>
-      </c>
-      <c r="D37" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920386</v>
-      </c>
-      <c r="B38" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" t="s">
-        <v>121</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920386</v>
-      </c>
-      <c r="B39" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" t="s">
-        <v>95</v>
-      </c>
-      <c r="D39" t="s">
-        <v>121</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920386</v>
-      </c>
-      <c r="B40" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920199</v>
-      </c>
-      <c r="B41" t="s">
-        <v>69</v>
-      </c>
-      <c r="C41" t="s">
-        <v>96</v>
-      </c>
-      <c r="D41" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920199</v>
-      </c>
-      <c r="B42" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" t="s">
-        <v>96</v>
-      </c>
-      <c r="D42" t="s">
-        <v>122</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920199</v>
-      </c>
-      <c r="B43" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" t="s">
-        <v>96</v>
-      </c>
-      <c r="D43" t="s">
-        <v>122</v>
-      </c>
-      <c r="E43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920201</v>
-      </c>
-      <c r="B44" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D44" t="s">
-        <v>123</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920201</v>
-      </c>
-      <c r="B45" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" t="s">
-        <v>97</v>
-      </c>
-      <c r="D45" t="s">
-        <v>123</v>
-      </c>
-      <c r="E45" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920201</v>
-      </c>
-      <c r="B46" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" t="s">
-        <v>97</v>
-      </c>
-      <c r="D46" t="s">
-        <v>123</v>
-      </c>
-      <c r="E46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920202</v>
-      </c>
-      <c r="B47" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" t="s">
-        <v>98</v>
-      </c>
-      <c r="D47" t="s">
-        <v>124</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920202</v>
-      </c>
-      <c r="B48" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" t="s">
-        <v>98</v>
-      </c>
-      <c r="D48" t="s">
-        <v>124</v>
-      </c>
-      <c r="E48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920202</v>
-      </c>
-      <c r="B49" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" t="s">
-        <v>124</v>
-      </c>
-      <c r="E49" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920203</v>
-      </c>
-      <c r="B50" t="s">
-        <v>72</v>
-      </c>
-      <c r="C50" t="s">
-        <v>99</v>
-      </c>
-      <c r="D50" t="s">
-        <v>125</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920203</v>
-      </c>
-      <c r="B51" t="s">
-        <v>72</v>
-      </c>
-      <c r="C51" t="s">
-        <v>99</v>
-      </c>
-      <c r="D51" t="s">
-        <v>125</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920203</v>
-      </c>
-      <c r="B52" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" t="s">
-        <v>99</v>
-      </c>
-      <c r="D52" t="s">
-        <v>125</v>
-      </c>
-      <c r="E52" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920204</v>
-      </c>
-      <c r="B53" t="s">
-        <v>73</v>
-      </c>
-      <c r="C53" t="s">
-        <v>100</v>
-      </c>
-      <c r="D53" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920204</v>
-      </c>
-      <c r="B54" t="s">
-        <v>73</v>
-      </c>
-      <c r="C54" t="s">
-        <v>100</v>
-      </c>
-      <c r="D54" t="s">
-        <v>126</v>
-      </c>
-      <c r="E54" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920204</v>
-      </c>
-      <c r="B55" t="s">
-        <v>73</v>
-      </c>
-      <c r="C55" t="s">
-        <v>100</v>
-      </c>
-      <c r="D55" t="s">
-        <v>126</v>
-      </c>
-      <c r="E55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920205</v>
-      </c>
-      <c r="B56" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" t="s">
-        <v>101</v>
-      </c>
-      <c r="D56" t="s">
-        <v>127</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920205</v>
-      </c>
-      <c r="B57" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" t="s">
-        <v>101</v>
-      </c>
-      <c r="D57" t="s">
-        <v>127</v>
-      </c>
-      <c r="E57" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920205</v>
-      </c>
-      <c r="B58" t="s">
-        <v>74</v>
-      </c>
-      <c r="C58" t="s">
-        <v>101</v>
-      </c>
-      <c r="D58" t="s">
-        <v>127</v>
-      </c>
-      <c r="E58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920206</v>
-      </c>
-      <c r="B59" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" t="s">
-        <v>102</v>
-      </c>
-      <c r="D59" t="s">
-        <v>128</v>
-      </c>
-      <c r="E59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920206</v>
-      </c>
-      <c r="B60" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60" t="s">
-        <v>102</v>
-      </c>
-      <c r="D60" t="s">
-        <v>128</v>
-      </c>
-      <c r="E60" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920206</v>
-      </c>
-      <c r="B61" t="s">
-        <v>75</v>
-      </c>
-      <c r="C61" t="s">
-        <v>102</v>
-      </c>
-      <c r="D61" t="s">
-        <v>128</v>
-      </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920207</v>
-      </c>
-      <c r="B62" t="s">
-        <v>76</v>
-      </c>
-      <c r="C62" t="s">
-        <v>79</v>
-      </c>
-      <c r="D62" t="s">
-        <v>129</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920207</v>
-      </c>
-      <c r="B63" t="s">
-        <v>76</v>
-      </c>
-      <c r="C63" t="s">
-        <v>79</v>
-      </c>
-      <c r="D63" t="s">
-        <v>129</v>
-      </c>
-      <c r="E63" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920207</v>
-      </c>
-      <c r="B64" t="s">
-        <v>76</v>
-      </c>
-      <c r="C64" t="s">
-        <v>79</v>
-      </c>
-      <c r="D64" t="s">
-        <v>129</v>
-      </c>
-      <c r="E64" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920208</v>
-      </c>
-      <c r="B65" t="s">
-        <v>77</v>
-      </c>
-      <c r="C65" t="s">
-        <v>89</v>
-      </c>
-      <c r="D65" t="s">
-        <v>130</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920208</v>
-      </c>
-      <c r="B66" t="s">
-        <v>77</v>
-      </c>
-      <c r="C66" t="s">
-        <v>89</v>
-      </c>
-      <c r="D66" t="s">
-        <v>130</v>
-      </c>
-      <c r="E66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920208</v>
-      </c>
-      <c r="B67" t="s">
-        <v>77</v>
-      </c>
-      <c r="C67" t="s">
-        <v>89</v>
-      </c>
-      <c r="D67" t="s">
-        <v>130</v>
-      </c>
-      <c r="E67" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920209</v>
-      </c>
-      <c r="B68" t="s">
-        <v>78</v>
-      </c>
-      <c r="C68" t="s">
-        <v>103</v>
-      </c>
-      <c r="D68" t="s">
-        <v>131</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920209</v>
-      </c>
-      <c r="B69" t="s">
-        <v>78</v>
-      </c>
-      <c r="C69" t="s">
-        <v>103</v>
-      </c>
-      <c r="D69" t="s">
-        <v>131</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920209</v>
-      </c>
-      <c r="B70" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" t="s">
-        <v>103</v>
-      </c>
-      <c r="D70" t="s">
-        <v>131</v>
-      </c>
-      <c r="E70" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920210</v>
-      </c>
-      <c r="B71" t="s">
-        <v>79</v>
-      </c>
-      <c r="C71" t="s">
-        <v>104</v>
-      </c>
-      <c r="D71" t="s">
-        <v>132</v>
-      </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920210</v>
-      </c>
-      <c r="B72" t="s">
-        <v>79</v>
-      </c>
-      <c r="C72" t="s">
-        <v>104</v>
-      </c>
-      <c r="D72" t="s">
-        <v>132</v>
-      </c>
-      <c r="E72" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920210</v>
-      </c>
-      <c r="B73" t="s">
-        <v>79</v>
-      </c>
-      <c r="C73" t="s">
-        <v>104</v>
-      </c>
-      <c r="D73" t="s">
-        <v>132</v>
-      </c>
-      <c r="E73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920211</v>
-      </c>
-      <c r="B74" t="s">
-        <v>80</v>
-      </c>
-      <c r="C74" t="s">
-        <v>91</v>
-      </c>
-      <c r="D74" t="s">
-        <v>133</v>
-      </c>
-      <c r="E74" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920211</v>
-      </c>
-      <c r="B75" t="s">
-        <v>80</v>
-      </c>
-      <c r="C75" t="s">
-        <v>91</v>
-      </c>
-      <c r="D75" t="s">
-        <v>133</v>
-      </c>
-      <c r="E75" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920211</v>
-      </c>
-      <c r="B76" t="s">
-        <v>80</v>
-      </c>
-      <c r="C76" t="s">
-        <v>91</v>
-      </c>
-      <c r="D76" t="s">
-        <v>133</v>
-      </c>
-      <c r="E76" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920212</v>
-      </c>
-      <c r="B77" t="s">
-        <v>81</v>
-      </c>
-      <c r="C77" t="s">
-        <v>105</v>
-      </c>
-      <c r="D77" t="s">
-        <v>134</v>
-      </c>
-      <c r="E77" t="s">
-        <v>7</v>
-      </c>
-      <c r="F77" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920212</v>
-      </c>
-      <c r="B78" t="s">
-        <v>81</v>
-      </c>
-      <c r="C78" t="s">
-        <v>105</v>
-      </c>
-      <c r="D78" t="s">
-        <v>134</v>
-      </c>
-      <c r="E78" t="s">
-        <v>5</v>
-      </c>
-      <c r="F78" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920212</v>
-      </c>
-      <c r="B79" t="s">
-        <v>81</v>
-      </c>
-      <c r="C79" t="s">
-        <v>105</v>
-      </c>
-      <c r="D79" t="s">
-        <v>134</v>
-      </c>
-      <c r="E79" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920213</v>
-      </c>
-      <c r="B80" t="s">
-        <v>82</v>
-      </c>
-      <c r="C80" t="s">
-        <v>106</v>
-      </c>
-      <c r="D80" t="s">
-        <v>135</v>
-      </c>
-      <c r="E80" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920213</v>
-      </c>
-      <c r="B81" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" t="s">
-        <v>106</v>
-      </c>
-      <c r="D81" t="s">
-        <v>135</v>
-      </c>
-      <c r="E81" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920213</v>
-      </c>
-      <c r="B82" t="s">
-        <v>82</v>
-      </c>
-      <c r="C82" t="s">
-        <v>106</v>
-      </c>
-      <c r="D82" t="s">
-        <v>135</v>
-      </c>
-      <c r="E82" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920214</v>
-      </c>
-      <c r="B83" t="s">
-        <v>83</v>
-      </c>
-      <c r="C83" t="s">
-        <v>107</v>
-      </c>
-      <c r="D83" t="s">
-        <v>136</v>
-      </c>
-      <c r="E83" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920214</v>
-      </c>
-      <c r="B84" t="s">
-        <v>83</v>
-      </c>
-      <c r="C84" t="s">
-        <v>107</v>
-      </c>
-      <c r="D84" t="s">
-        <v>136</v>
-      </c>
-      <c r="E84" t="s">
-        <v>5</v>
-      </c>
-      <c r="F84" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920214</v>
-      </c>
-      <c r="B85" t="s">
-        <v>83</v>
-      </c>
-      <c r="C85" t="s">
-        <v>107</v>
-      </c>
-      <c r="D85" t="s">
-        <v>136</v>
-      </c>
-      <c r="E85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>20330051920386</v>
-      </c>
-      <c r="B86" t="s">
-        <v>84</v>
-      </c>
-      <c r="C86" t="s">
-        <v>108</v>
-      </c>
-      <c r="D86" t="s">
-        <v>137</v>
-      </c>
-      <c r="E86" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" t="s">
         <v>54</v>
       </c>
     </row>
@@ -7558,13 +6424,13 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7575,13 +6441,13 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7592,13 +6458,13 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7609,13 +6475,13 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7626,13 +6492,13 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7643,13 +6509,13 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7660,13 +6526,13 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7680,10 +6546,10 @@
         <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7694,13 +6560,13 @@
         <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7711,13 +6577,13 @@
         <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7728,13 +6594,13 @@
         <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7748,10 +6614,10 @@
         <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7762,13 +6628,13 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7779,13 +6645,13 @@
         <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7796,13 +6662,13 @@
         <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7813,13 +6679,13 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7830,13 +6696,13 @@
         <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7847,13 +6713,13 @@
         <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7864,13 +6730,13 @@
         <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7881,13 +6747,13 @@
         <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7901,10 +6767,10 @@
         <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7915,13 +6781,13 @@
         <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7932,13 +6798,13 @@
         <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7949,13 +6815,13 @@
         <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7966,13 +6832,13 @@
         <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7983,13 +6849,13 @@
         <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8000,13 +6866,13 @@
         <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8017,13 +6883,13 @@
         <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8031,16 +6897,16 @@
         <v>20330051920386</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="D30" t="s">
         <v>137</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8050,7 +6916,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8082,24 +6948,461 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920386</v>
+        <v>21330051920187</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>54</v>
       </c>
       <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920187</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920193</v>
+      </c>
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920193</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920212</v>
+      </c>
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920212</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920185</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920186</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920189</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920191</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920192</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920194</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920196</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920204</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920205</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920206</v>
+      </c>
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920208</v>
+      </c>
+      <c r="B18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920210</v>
+      </c>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920211</v>
+      </c>
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920214</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4BEM - Estadisticos 20222.xlsx
+++ b/grupos/4BEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="138">
   <si>
     <t>Materia</t>
   </si>
@@ -273,6 +273,9 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
     <t>DOLORES</t>
   </si>
   <si>
@@ -342,6 +345,9 @@
     <t>CUICAHUA</t>
   </si>
   <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
     <t>MIGUEL ANGEL</t>
   </si>
   <si>
@@ -424,12 +430,6 @@
   </si>
   <si>
     <t>DARINKA</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
   </si>
   <si>
     <t>YAEL</t>
@@ -940,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -1003,7 +1003,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -1029,7 +1029,7 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>9</v>
@@ -1092,7 +1092,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>9</v>
@@ -1118,7 +1118,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -1181,7 +1181,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>10</v>
@@ -1207,7 +1207,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1270,7 +1270,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1296,7 +1296,7 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>9</v>
@@ -1359,7 +1359,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>9</v>
@@ -1385,7 +1385,7 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -1448,7 +1448,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1537,7 +1537,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -1626,7 +1626,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>6</v>
@@ -1652,7 +1652,7 @@
         <v>9</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -1715,7 +1715,7 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -1741,7 +1741,7 @@
         <v>9</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -1804,7 +1804,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1830,7 +1830,7 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>7</v>
@@ -1893,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -1919,7 +1919,7 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -1982,7 +1982,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>6</v>
@@ -2008,7 +2008,7 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>5</v>
@@ -2071,7 +2071,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -2097,7 +2097,7 @@
         <v>5</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -2160,7 +2160,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>5</v>
@@ -2186,7 +2186,7 @@
         <v>5</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>5</v>
@@ -2249,7 +2249,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -2275,7 +2275,7 @@
         <v>5</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -2338,7 +2338,7 @@
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z19">
         <v>5</v>
@@ -2364,7 +2364,7 @@
         <v>9</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -2427,7 +2427,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>10</v>
@@ -2453,7 +2453,7 @@
         <v>10</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E21">
         <v>8</v>
@@ -2516,7 +2516,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>8</v>
@@ -2542,7 +2542,7 @@
         <v>9</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>7</v>
@@ -2605,7 +2605,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -2631,7 +2631,7 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>6</v>
@@ -2694,7 +2694,7 @@
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <v>6</v>
@@ -2720,7 +2720,7 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -2783,7 +2783,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>10</v>
@@ -2809,7 +2809,7 @@
         <v>10</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -2872,7 +2872,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>6</v>
@@ -2898,7 +2898,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>6</v>
@@ -2961,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z26">
         <v>6</v>
@@ -2987,7 +2987,7 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>10</v>
@@ -3050,7 +3050,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>10</v>
@@ -3076,7 +3076,7 @@
         <v>9</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E28">
         <v>10</v>
@@ -3139,7 +3139,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z28">
         <v>10</v>
@@ -3165,7 +3165,7 @@
         <v>8</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>7</v>
@@ -3228,7 +3228,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z29">
         <v>7</v>
@@ -3254,7 +3254,7 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E30">
         <v>6</v>
@@ -3317,7 +3317,7 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z30">
         <v>6</v>
@@ -3343,7 +3343,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>10</v>
@@ -3406,7 +3406,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z31">
         <v>10</v>
@@ -3595,7 +3595,7 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>106.7</v>
@@ -3663,7 +3663,7 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>106.7</v>
@@ -3731,7 +3731,7 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>106.7</v>
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>106.7</v>
@@ -3935,7 +3935,7 @@
         <v>70</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>106.7</v>
@@ -4003,7 +4003,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>106.7</v>
@@ -4071,7 +4071,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>106.7</v>
@@ -4139,7 +4139,7 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>106.7</v>
@@ -4207,7 +4207,7 @@
         <v>80</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>106.7</v>
@@ -4275,7 +4275,7 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>106.7</v>
@@ -4343,7 +4343,7 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>106.7</v>
@@ -4411,7 +4411,7 @@
         <v>70</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>106.7</v>
@@ -4479,7 +4479,7 @@
         <v>70</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>106.7</v>
@@ -4547,7 +4547,7 @@
         <v>70</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>106.7</v>
@@ -4615,7 +4615,7 @@
         <v>70</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4683,7 +4683,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>106.7</v>
@@ -4751,7 +4751,7 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>106.7</v>
@@ -4819,7 +4819,7 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>106.7</v>
@@ -4887,7 +4887,7 @@
         <v>50</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E23">
         <v>106.7</v>
@@ -4955,7 +4955,7 @@
         <v>100</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>106.7</v>
@@ -5023,7 +5023,7 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>106.7</v>
@@ -5091,7 +5091,7 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>106.7</v>
@@ -5159,7 +5159,7 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>106.7</v>
@@ -5227,7 +5227,7 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>106.7</v>
@@ -5295,7 +5295,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>106.7</v>
@@ -5363,7 +5363,7 @@
         <v>60</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E30">
         <v>106.7</v>
@@ -5431,7 +5431,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>106.7</v>
@@ -5572,57 +5572,60 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>62.07</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>37.93</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
       <c r="I2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>18</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>62.07</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G3">
-        <v>37.93</v>
+        <v>35.71</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5633,7 +5636,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -5642,19 +5645,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>64.29000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G4">
-        <v>35.71</v>
+        <v>28.57</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5665,28 +5668,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>71.43000000000001</v>
+        <v>75.86</v>
       </c>
       <c r="G5">
-        <v>28.57</v>
+        <v>24.14</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5697,28 +5700,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>22</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>75.86</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="G6">
-        <v>24.14</v>
+        <v>21.43</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5798,7 +5801,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5823,566 +5826,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920185</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920186</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920187</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920188</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920189</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920190</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920191</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920192</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920193</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330061430023</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920194</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920196</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920386</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920199</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920201</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>121</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920202</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920203</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920204</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920205</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" t="s">
-        <v>125</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920206</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920207</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920208</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920209</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920210</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" t="s">
-        <v>130</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920211</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" t="s">
-        <v>131</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920212</v>
-      </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" t="s">
-        <v>132</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920213</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" t="s">
-        <v>133</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920214</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" t="s">
-        <v>134</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -6424,13 +5867,13 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6441,13 +5884,13 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6458,13 +5901,13 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6475,13 +5918,13 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6492,13 +5935,13 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6509,13 +5952,13 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6526,13 +5969,13 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6546,10 +5989,10 @@
         <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6560,13 +6003,13 @@
         <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6577,13 +6020,13 @@
         <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6594,13 +6037,13 @@
         <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6614,10 +6057,10 @@
         <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6628,13 +6071,13 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6645,13 +6088,13 @@
         <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6662,13 +6105,13 @@
         <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6679,13 +6122,13 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6696,13 +6139,13 @@
         <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6713,13 +6156,13 @@
         <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6730,13 +6173,13 @@
         <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6747,13 +6190,13 @@
         <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6767,10 +6210,10 @@
         <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6781,13 +6224,13 @@
         <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6798,13 +6241,13 @@
         <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6815,13 +6258,13 @@
         <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6832,13 +6275,13 @@
         <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6849,13 +6292,13 @@
         <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6866,13 +6309,13 @@
         <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6883,13 +6326,13 @@
         <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6897,10 +6340,10 @@
         <v>20330051920386</v>
       </c>
       <c r="B30" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
         <v>137</v>
@@ -6916,7 +6359,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6948,16 +6391,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920187</v>
+        <v>21330051920203</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6971,65 +6414,65 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920187</v>
+        <v>21330051920203</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920193</v>
+        <v>21330051920187</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920193</v>
+        <v>21330051920189</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>54</v>
@@ -7040,19 +6483,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920212</v>
+        <v>21330051920193</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
@@ -7069,341 +6512,19 @@
         <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920185</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920186</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920189</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920191</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920192</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920194</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920196</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920204</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920205</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>125</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920206</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920208</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" t="s">
-        <v>128</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920210</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920211</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" t="s">
-        <v>131</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920214</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4BEM - Estadisticos 20222.xlsx
+++ b/grupos/4BEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="144">
   <si>
     <t>Materia</t>
   </si>
@@ -183,7 +183,25 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>NC</t>
@@ -5607,7 +5625,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3">
         <v>28</v>
@@ -5639,7 +5657,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4">
         <v>28</v>
@@ -5671,7 +5689,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>29</v>
@@ -5703,7 +5721,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>28</v>
@@ -5735,7 +5753,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>28</v>
@@ -5767,7 +5785,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>29</v>
@@ -5810,16 +5828,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5844,16 +5862,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>52</v>
@@ -5864,13 +5882,13 @@
         <v>21330051920185</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5881,13 +5899,13 @@
         <v>21330051920186</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -5898,13 +5916,13 @@
         <v>21330051920187</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -5915,13 +5933,13 @@
         <v>21330051920188</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -5932,13 +5950,13 @@
         <v>21330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5949,13 +5967,13 @@
         <v>21330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5966,13 +5984,13 @@
         <v>21330051920191</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5983,13 +6001,13 @@
         <v>21330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6000,13 +6018,13 @@
         <v>21330051920193</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6017,13 +6035,13 @@
         <v>19330061430023</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6034,13 +6052,13 @@
         <v>21330051920194</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6051,13 +6069,13 @@
         <v>21330051920196</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6068,13 +6086,13 @@
         <v>21330051920386</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6085,13 +6103,13 @@
         <v>21330051920199</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6102,13 +6120,13 @@
         <v>21330051920201</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6119,13 +6137,13 @@
         <v>21330051920202</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6136,13 +6154,13 @@
         <v>21330051920203</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6153,13 +6171,13 @@
         <v>21330051920204</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6170,13 +6188,13 @@
         <v>21330051920205</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6187,13 +6205,13 @@
         <v>21330051920206</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6204,13 +6222,13 @@
         <v>21330051920207</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6221,13 +6239,13 @@
         <v>21330051920208</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6238,13 +6256,13 @@
         <v>21330051920209</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6255,13 +6273,13 @@
         <v>21330051920210</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6272,13 +6290,13 @@
         <v>21330051920211</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6289,13 +6307,13 @@
         <v>21330051920212</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6306,13 +6324,13 @@
         <v>21330051920213</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6323,13 +6341,13 @@
         <v>21330051920214</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6340,13 +6358,13 @@
         <v>20330051920386</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6368,16 +6386,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6394,19 +6412,19 @@
         <v>21330051920203</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6417,13 +6435,13 @@
         <v>21330051920203</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6440,19 +6458,19 @@
         <v>21330051920187</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6463,19 +6481,19 @@
         <v>21330051920189</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6486,13 +6504,13 @@
         <v>21330051920193</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -6509,19 +6527,19 @@
         <v>21330051920212</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>

--- a/grupos/4BEM - Estadisticos 20222.xlsx
+++ b/grupos/4BEM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -189,18 +188,18 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
@@ -216,247 +215,67 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
   </si>
   <si>
     <t>BERNABE</t>
   </si>
   <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>CHULIN</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ELVIRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>QUIJANO</t>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>RICO</t>
   </si>
   <si>
-    <t>ROSALIANO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>PEDRO EVER</t>
+    <t>ANGEL ALDAIR</t>
+  </si>
+  <si>
+    <t>SINAI ANTONIO</t>
+  </si>
+  <si>
+    <t>JORGE MARIO</t>
   </si>
   <si>
     <t>NEIL</t>
   </si>
   <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAIR</t>
-  </si>
-  <si>
     <t>JORGE GUILLERMO</t>
   </si>
   <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
     <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>CELSO ALEJANDRO</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>DIEGO HUMBERTO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
-  </si>
-  <si>
-    <t>ZURIEL ELIHU</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>ARIEL CHARBEL</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>DARINKA</t>
-  </si>
-  <si>
-    <t>YAEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -509,11 +328,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -973,25 +793,25 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1015,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1030,10 +850,10 @@
         <v>10</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1062,25 +882,25 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1104,25 +924,25 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>6</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA5">
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1151,25 +971,25 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1202,16 +1022,16 @@
         <v>6</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1240,25 +1060,25 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1329,25 +1149,25 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1371,7 +1191,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1380,16 +1200,16 @@
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1418,25 +1238,25 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1460,25 +1280,25 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1507,25 +1327,25 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1561,13 +1381,13 @@
         <v>10</v>
       </c>
       <c r="AA10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB10">
         <v>9</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1596,25 +1416,25 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1641,7 +1461,7 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -1650,13 +1470,13 @@
         <v>6</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1685,25 +1505,25 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1727,25 +1547,25 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>6</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB12">
         <v>5</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1774,25 +1594,25 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1819,7 +1639,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1863,25 +1683,25 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1905,7 +1725,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1914,7 +1734,7 @@
         <v>6</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1923,7 +1743,7 @@
         <v>9</v>
       </c>
       <c r="AC14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1952,25 +1772,25 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1997,19 +1817,19 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>6</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -2041,25 +1861,25 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2083,7 +1903,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -2095,13 +1915,13 @@
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB16">
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2130,25 +1950,25 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2190,7 +2010,7 @@
         <v>5</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2201,7 +2021,7 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -2219,25 +2039,25 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2261,10 +2081,10 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2273,10 +2093,10 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>6</v>
@@ -2308,25 +2128,25 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2362,10 +2182,10 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -2397,25 +2217,25 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2448,7 +2268,7 @@
         <v>6</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>8</v>
@@ -2457,7 +2277,7 @@
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2486,25 +2306,25 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2528,7 +2348,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -2537,16 +2357,16 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB21">
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2575,25 +2395,25 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2626,16 +2446,16 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2664,25 +2484,25 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2706,25 +2526,25 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>5</v>
       </c>
       <c r="AC23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2753,25 +2573,25 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2813,7 +2633,7 @@
         <v>8</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2842,25 +2662,25 @@
         <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2893,16 +2713,16 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>10</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2931,25 +2751,25 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2976,22 +2796,22 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>6</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <v>5</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3020,25 +2840,25 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3062,7 +2882,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -3074,13 +2894,13 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB27">
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3109,25 +2929,25 @@
         <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3151,7 +2971,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -3169,7 +2989,7 @@
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3198,25 +3018,25 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3240,7 +3060,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -3255,10 +3075,10 @@
         <v>9</v>
       </c>
       <c r="AB29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3287,25 +3107,25 @@
         <v>5</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3332,7 +3152,7 @@
         <v>5</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -3347,7 +3167,7 @@
         <v>5</v>
       </c>
       <c r="AC30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3376,25 +3196,25 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3436,7 +3256,7 @@
         <v>9</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3453,13 +3273,13 @@
         <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>-1</v>
@@ -3471,10 +3291,10 @@
         <v>-1</v>
       </c>
       <c r="AA32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC32">
         <v>8</v>
@@ -3628,25 +3448,25 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -3696,25 +3516,25 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -3764,25 +3584,25 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -3900,25 +3720,25 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -3968,25 +3788,25 @@
         <v>90</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -4036,25 +3856,25 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -4104,25 +3924,25 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -4172,10 +3992,10 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -4184,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -4240,25 +4060,25 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -4308,25 +4128,25 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4376,25 +4196,25 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -4444,25 +4264,25 @@
         <v>83.3</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -4512,25 +4332,25 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4580,25 +4400,25 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4648,25 +4468,25 @@
         <v>80</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4716,25 +4536,25 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4784,25 +4604,25 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4852,25 +4672,25 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -4920,25 +4740,25 @@
         <v>83.3</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -4988,25 +4808,25 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -5056,25 +4876,25 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -5124,25 +4944,25 @@
         <v>80</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5192,25 +5012,25 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5260,25 +5080,25 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -5328,25 +5148,25 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -5396,25 +5216,25 @@
         <v>93.3</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -5464,25 +5284,25 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -5520,13 +5340,13 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T32">
         <v>0</v>
@@ -5554,6 +5374,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5599,24 +5421,24 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>11</v>
-      </c>
-      <c r="F2">
-        <v>62.07</v>
-      </c>
-      <c r="G2">
-        <v>37.93</v>
+        <v>12</v>
+      </c>
+      <c r="F2" s="2">
+        <v>58.6</v>
+      </c>
+      <c r="G2" s="2">
+        <v>41.4</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5636,25 +5458,25 @@
       <c r="E3">
         <v>10</v>
       </c>
-      <c r="F3">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="G3">
-        <v>35.71</v>
+      <c r="F3" s="2">
+        <v>64.3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>35.7</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5663,62 +5485,62 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>8</v>
-      </c>
-      <c r="F4">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="G4">
-        <v>28.57</v>
+        <v>7</v>
+      </c>
+      <c r="F4" s="2">
+        <v>75</v>
+      </c>
+      <c r="G4" s="2">
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>22</v>
       </c>
       <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>75.86</v>
-      </c>
-      <c r="G5">
-        <v>24.14</v>
+        <v>6</v>
+      </c>
+      <c r="F5" s="2">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="G5" s="2">
+        <v>21.4</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5727,48 +5549,48 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="G6">
-        <v>21.43</v>
+        <v>4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>85.7</v>
+      </c>
+      <c r="G6" s="2">
+        <v>14.3</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="G7">
-        <v>21.43</v>
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>86.2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>13.8</v>
       </c>
       <c r="H7">
         <v>7.4</v>
@@ -5776,7 +5598,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5791,24 +5613,24 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="G8">
-        <v>6.9</v>
+        <v>4</v>
+      </c>
+      <c r="F8" s="2">
+        <v>86.2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>13.8</v>
       </c>
       <c r="H8">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5853,531 +5675,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920185</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>21330051920186</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>21330051920187</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>21330051920188</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>21330051920189</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>21330051920190</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>21330051920191</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>21330051920192</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>21330051920193</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>19330061430023</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>21330051920194</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>21330051920196</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>21330051920386</v>
-      </c>
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>21330051920199</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>21330051920201</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>21330051920202</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" t="s">
-        <v>130</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>21330051920203</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>21330051920204</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>21330051920205</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>21330051920206</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21330051920207</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>21330051920208</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" t="s">
-        <v>136</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>21330051920209</v>
-      </c>
-      <c r="B24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>21330051920210</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>21330051920211</v>
-      </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>21330051920212</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>21330051920213</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>21330051920214</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29" t="s">
-        <v>142</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>20330051920386</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" t="s">
-        <v>143</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6409,16 +5707,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920203</v>
+        <v>21330051920189</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6432,22 +5730,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920203</v>
+        <v>21330051920189</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6455,22 +5753,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920187</v>
+        <v>21330051920207</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6478,22 +5776,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920189</v>
+        <v>21330051920207</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6501,22 +5799,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920193</v>
+        <v>21330051920209</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6524,24 +5822,93 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920212</v>
+        <v>21330051920209</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920187</v>
+      </c>
+      <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
         <v>55</v>
       </c>
-      <c r="G7">
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920190</v>
+      </c>
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920192</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BEM - Estadisticos 20222.xlsx
+++ b/grupos/4BEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -185,15 +185,15 @@
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -218,55 +218,64 @@
     <t>BONILLA</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CHULIN</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
     <t>ANGEL ALDAIR</t>
   </si>
   <si>
+    <t>JORGE MARIO</t>
+  </si>
+  <si>
+    <t>PEDRO EVER</t>
+  </si>
+  <si>
+    <t>NEIL</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
+  </si>
+  <si>
     <t>SINAI ANTONIO</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
   </si>
 </sst>
 </file>
@@ -799,7 +808,7 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -841,7 +850,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -888,7 +897,7 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -930,7 +939,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <v>10</v>
@@ -977,7 +986,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -1019,7 +1028,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z6">
         <v>9</v>
@@ -1066,7 +1075,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1108,7 +1117,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1155,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1244,7 +1253,7 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1333,7 +1342,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1422,7 +1431,7 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -1464,7 +1473,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z11">
         <v>6</v>
@@ -1511,7 +1520,7 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -1553,7 +1562,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1600,7 +1609,7 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -1689,7 +1698,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -1731,7 +1740,7 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>9</v>
@@ -1778,7 +1787,7 @@
         <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -1820,7 +1829,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>8</v>
@@ -1867,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -1909,7 +1918,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -1956,7 +1965,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -1998,7 +2007,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z17">
         <v>5</v>
@@ -2045,7 +2054,7 @@
         <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>6</v>
@@ -2134,7 +2143,7 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -2223,7 +2232,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -2265,7 +2274,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <v>9</v>
@@ -2312,7 +2321,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2354,7 +2363,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>9</v>
@@ -2401,7 +2410,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>8</v>
@@ -2490,7 +2499,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2532,7 +2541,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z23">
         <v>8</v>
@@ -2579,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2621,7 +2630,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z24">
         <v>10</v>
@@ -2668,7 +2677,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>8</v>
@@ -2710,7 +2719,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>7</v>
@@ -2757,7 +2766,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>7</v>
@@ -2846,7 +2855,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -2935,7 +2944,7 @@
         <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -2977,7 +2986,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>10</v>
@@ -3024,7 +3033,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>6</v>
@@ -3066,7 +3075,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <v>7</v>
@@ -3113,7 +3122,7 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>6</v>
@@ -3202,7 +3211,7 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -3244,7 +3253,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z31">
         <v>10</v>
@@ -3454,7 +3463,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>106.7</v>
@@ -3522,7 +3531,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>106.7</v>
@@ -3590,7 +3599,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>106.7</v>
@@ -3726,7 +3735,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L8">
         <v>106.7</v>
@@ -3794,7 +3803,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>106.7</v>
@@ -3862,7 +3871,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>106.7</v>
@@ -3930,7 +3939,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>106.7</v>
@@ -4066,7 +4075,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>106.7</v>
@@ -4134,7 +4143,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>106.7</v>
@@ -4202,7 +4211,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>106.7</v>
@@ -4270,7 +4279,7 @@
         <v>70</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L16">
         <v>106.7</v>
@@ -4338,7 +4347,7 @@
         <v>85</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>106.7</v>
@@ -4406,7 +4415,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L18">
         <v>106.7</v>
@@ -4474,7 +4483,7 @@
         <v>70</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>66.7</v>
@@ -4542,7 +4551,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L20">
         <v>106.7</v>
@@ -4610,7 +4619,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>106.7</v>
@@ -4678,7 +4687,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>106.7</v>
@@ -4746,7 +4755,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>106.7</v>
@@ -4814,7 +4823,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>106.7</v>
@@ -4882,7 +4891,7 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>106.7</v>
@@ -4950,7 +4959,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>106.7</v>
@@ -5018,7 +5027,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>106.7</v>
@@ -5086,7 +5095,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>106.7</v>
@@ -5154,7 +5163,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>106.7</v>
@@ -5222,7 +5231,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>106.7</v>
@@ -5290,7 +5299,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>106.7</v>
@@ -5444,7 +5453,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5453,19 +5462,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>64.3</v>
+        <v>60.7</v>
       </c>
       <c r="G3" s="2">
-        <v>35.7</v>
+        <v>39.3</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5476,7 +5485,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5485,19 +5494,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>75</v>
+        <v>64.3</v>
       </c>
       <c r="G4" s="2">
-        <v>25</v>
+        <v>35.7</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5508,7 +5517,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5517,19 +5526,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>78.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="G5" s="2">
-        <v>21.4</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5713,16 +5722,16 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5736,16 +5745,16 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5753,22 +5762,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920207</v>
+        <v>21330051920209</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5776,16 +5785,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920207</v>
+        <v>21330051920209</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5799,19 +5808,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920209</v>
+        <v>21330051920186</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>55</v>
@@ -5822,22 +5831,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920209</v>
+        <v>21330051920187</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5845,22 +5854,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920187</v>
+        <v>21330051920190</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5868,16 +5877,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920190</v>
+        <v>21330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5891,16 +5900,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920192</v>
+        <v>21330051920207</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>

--- a/grupos/4BEM - Estadisticos 20222.xlsx
+++ b/grupos/4BEM - Estadisticos 20222.xlsx
@@ -3445,13 +3445,13 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>100</v>
@@ -3466,37 +3466,37 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N4">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3513,19 +3513,19 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G5">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3534,37 +3534,37 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>83.3</v>
+        <v>98</v>
       </c>
       <c r="N5">
-        <v>80</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3581,13 +3581,13 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G6">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>100</v>
@@ -3602,37 +3602,37 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>83.3</v>
+        <v>98</v>
       </c>
       <c r="N6">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3661,46 +3661,46 @@
         <v>90</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N7">
         <v>0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U7">
         <v>0</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3717,58 +3717,58 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G8">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L8">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>83.3</v>
+        <v>98</v>
       </c>
       <c r="N8">
-        <v>73.3</v>
+        <v>92.2</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3785,58 +3785,58 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G9">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="H9">
         <v>90</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="N9">
-        <v>73.3</v>
+        <v>90.2</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3853,19 +3853,19 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G10">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3874,37 +3874,37 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N10">
-        <v>80</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3921,13 +3921,13 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G11">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -3942,37 +3942,37 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>76.7</v>
+        <v>96</v>
       </c>
       <c r="N11">
-        <v>76.7</v>
+        <v>92.2</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3989,58 +3989,58 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F12">
-        <v>73.3</v>
+        <v>88</v>
       </c>
       <c r="G12">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="H12">
         <v>100</v>
       </c>
       <c r="I12">
+        <v>67.5</v>
+      </c>
+      <c r="J12">
+        <v>75</v>
+      </c>
+      <c r="K12">
         <v>50</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>50</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
       <c r="M12">
-        <v>26.7</v>
+        <v>60</v>
       </c>
       <c r="N12">
-        <v>73.3</v>
+        <v>88.2</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4057,13 +4057,13 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>76.7</v>
+        <v>92</v>
       </c>
       <c r="G13">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="H13">
         <v>100</v>
@@ -4072,43 +4072,43 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>76.7</v>
+        <v>92</v>
       </c>
       <c r="N13">
-        <v>76.7</v>
+        <v>90.2</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4125,19 +4125,19 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G14">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -4146,37 +4146,37 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>83.3</v>
+        <v>98</v>
       </c>
       <c r="N14">
-        <v>80</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4193,19 +4193,19 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F15">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G15">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="H15">
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4214,37 +4214,37 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>76.7</v>
+        <v>94</v>
       </c>
       <c r="N15">
-        <v>76.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O15">
         <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4261,58 +4261,58 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F16">
-        <v>73.3</v>
+        <v>88</v>
       </c>
       <c r="G16">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="H16">
         <v>83.3</v>
       </c>
       <c r="I16">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J16">
         <v>70</v>
       </c>
       <c r="K16">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="L16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M16">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N16">
-        <v>73.3</v>
+        <v>88.2</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4329,58 +4329,58 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F17">
-        <v>73.3</v>
+        <v>88</v>
       </c>
       <c r="G17">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="J17">
-        <v>85</v>
+        <v>77.5</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M17">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="N17">
-        <v>73.3</v>
+        <v>88.2</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4397,58 +4397,58 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F18">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="G18">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="H18">
         <v>100</v>
       </c>
       <c r="I18">
+        <v>85</v>
+      </c>
+      <c r="J18">
+        <v>85</v>
+      </c>
+      <c r="K18">
         <v>90</v>
       </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
-      <c r="K18">
-        <v>80</v>
-      </c>
       <c r="L18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="N18">
-        <v>73.3</v>
+        <v>90.2</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4468,10 +4468,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>73.3</v>
+        <v>88</v>
       </c>
       <c r="G19">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="H19">
         <v>80</v>
@@ -4483,40 +4483,40 @@
         <v>70</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L19">
-        <v>66.7</v>
+        <v>31.3</v>
       </c>
       <c r="M19">
-        <v>53.3</v>
+        <v>76</v>
       </c>
       <c r="N19">
-        <v>80</v>
+        <v>92.2</v>
       </c>
       <c r="O19">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>31.3</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4533,58 +4533,58 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F20">
-        <v>73.3</v>
+        <v>88</v>
       </c>
       <c r="G20">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="H20">
         <v>100</v>
       </c>
       <c r="I20">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>66.7</v>
+        <v>84</v>
       </c>
       <c r="N20">
-        <v>80</v>
+        <v>92.2</v>
       </c>
       <c r="O20">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4601,13 +4601,13 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F21">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G21">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="H21">
         <v>100</v>
@@ -4622,37 +4622,37 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N21">
-        <v>80</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4669,19 +4669,19 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F22">
-        <v>76.7</v>
+        <v>92</v>
       </c>
       <c r="G22">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -4690,37 +4690,37 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>73.3</v>
+        <v>90</v>
       </c>
       <c r="N22">
-        <v>76.7</v>
+        <v>92.2</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4737,58 +4737,58 @@
         <v>90</v>
       </c>
       <c r="E23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F23">
-        <v>73.3</v>
+        <v>88</v>
       </c>
       <c r="G23">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="H23">
         <v>83.3</v>
       </c>
       <c r="I23">
+        <v>92.5</v>
+      </c>
+      <c r="J23">
+        <v>75</v>
+      </c>
+      <c r="K23">
         <v>95</v>
       </c>
-      <c r="J23">
-        <v>100</v>
-      </c>
-      <c r="K23">
-        <v>100</v>
-      </c>
       <c r="L23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>73.3</v>
+        <v>88</v>
       </c>
       <c r="N23">
-        <v>76.7</v>
+        <v>92.2</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4805,13 +4805,13 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F24">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G24">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="H24">
         <v>100</v>
@@ -4826,37 +4826,37 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>76.7</v>
+        <v>96</v>
       </c>
       <c r="N24">
-        <v>73.3</v>
+        <v>90.2</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4873,13 +4873,13 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F25">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G25">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="H25">
         <v>100</v>
@@ -4894,37 +4894,37 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>73.3</v>
+        <v>90.2</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -4941,58 +4941,58 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F26">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G26">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="H26">
         <v>80</v>
       </c>
       <c r="I26">
+        <v>85</v>
+      </c>
+      <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
+        <v>100</v>
+      </c>
+      <c r="M26">
+        <v>78</v>
+      </c>
+      <c r="N26">
+        <v>90.2</v>
+      </c>
+      <c r="O26">
         <v>90</v>
       </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
-      <c r="L26">
-        <v>106.7</v>
-      </c>
-      <c r="M26">
-        <v>60</v>
-      </c>
-      <c r="N26">
-        <v>76.7</v>
-      </c>
-      <c r="O26">
-        <v>100</v>
-      </c>
       <c r="P26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5009,19 +5009,19 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F27">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G27">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="H27">
         <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -5030,37 +5030,37 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>83.3</v>
+        <v>98</v>
       </c>
       <c r="N27">
-        <v>80</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O27">
         <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5077,13 +5077,13 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F28">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G28">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="H28">
         <v>100</v>
@@ -5098,37 +5098,37 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N28">
-        <v>80</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O28">
         <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5145,13 +5145,13 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F29">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G29">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="H29">
         <v>100</v>
@@ -5166,37 +5166,37 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="N29">
-        <v>73.3</v>
+        <v>92.2</v>
       </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5213,58 +5213,58 @@
         <v>90</v>
       </c>
       <c r="E30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G30">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="H30">
         <v>93.3</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J30">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N30">
-        <v>70</v>
+        <v>86.3</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>86.3</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5281,19 +5281,19 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F31">
-        <v>76.7</v>
+        <v>92</v>
       </c>
       <c r="G31">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="H31">
         <v>100</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J31">
         <v>100</v>
@@ -5302,37 +5302,37 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M31">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="N31">
-        <v>80</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O31">
         <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5340,31 +5340,31 @@
         <v>41</v>
       </c>
       <c r="F32">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G32">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="H32">
         <v>100</v>
       </c>
       <c r="M32">
-        <v>73.3</v>
+        <v>92</v>
       </c>
       <c r="N32">
-        <v>73.3</v>
+        <v>92.2</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4BEM - Estadisticos 20222.xlsx
+++ b/grupos/4BEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -182,27 +182,27 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,67 +215,85 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
     <t>NAVARRO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>NEIL</t>
   </si>
   <si>
     <t>ANGEL ALDAIR</t>
   </si>
   <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
     <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>PEDRO EVER</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -826,22 +844,22 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -856,7 +874,7 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB4">
         <v>9</v>
@@ -915,22 +933,22 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -939,7 +957,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>10</v>
@@ -1004,22 +1022,22 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1037,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1093,22 +1111,22 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1182,22 +1200,22 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1206,7 +1224,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z8">
         <v>10</v>
@@ -1215,10 +1233,10 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1250,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>6</v>
@@ -1271,28 +1289,28 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1301,10 +1319,10 @@
         <v>9</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC9">
         <v>7</v>
@@ -1360,22 +1378,22 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1390,7 +1408,7 @@
         <v>10</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB10">
         <v>9</v>
@@ -1449,22 +1467,22 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1482,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="AB11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1538,28 +1556,28 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1571,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1627,22 +1645,22 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1651,19 +1669,19 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1716,22 +1734,22 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1752,7 +1770,7 @@
         <v>9</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1805,28 +1823,28 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>6</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1835,10 +1853,10 @@
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -1894,22 +1912,22 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1918,16 +1936,16 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -1983,40 +2001,40 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>5</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC17">
         <v>8</v>
@@ -2072,22 +2090,22 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2096,7 +2114,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -2105,10 +2123,10 @@
         <v>7</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2161,22 +2179,22 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2185,7 +2203,7 @@
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>5</v>
@@ -2194,10 +2212,10 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2250,22 +2268,22 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2274,19 +2292,19 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>9</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2339,22 +2357,22 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2375,7 +2393,7 @@
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2428,22 +2446,22 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2458,10 +2476,10 @@
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -2517,22 +2535,22 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2547,10 +2565,10 @@
         <v>8</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC23">
         <v>6</v>
@@ -2606,22 +2624,22 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2630,7 +2648,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>10</v>
@@ -2639,7 +2657,7 @@
         <v>10</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC24">
         <v>9</v>
@@ -2695,22 +2713,22 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2719,13 +2737,13 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>7</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB25">
         <v>8</v>
@@ -2784,22 +2802,22 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>5</v>
@@ -2817,10 +2835,10 @@
         <v>6</v>
       </c>
       <c r="AB26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2873,22 +2891,22 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2903,7 +2921,7 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB27">
         <v>10</v>
@@ -2962,22 +2980,22 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -3051,22 +3069,22 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -3081,10 +3099,10 @@
         <v>7</v>
       </c>
       <c r="AA29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>8</v>
@@ -3140,22 +3158,22 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -3164,7 +3182,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z30">
         <v>6</v>
@@ -3173,7 +3191,7 @@
         <v>5</v>
       </c>
       <c r="AB30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC30">
         <v>6</v>
@@ -3229,37 +3247,37 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>7</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z31">
         <v>10</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB31">
         <v>9</v>
@@ -3291,22 +3309,22 @@
         <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA32">
         <v>8</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3558,10 +3576,10 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="U5">
-        <v>96.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3626,10 +3644,10 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="U6">
-        <v>98</v>
+        <v>97.7</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -3688,19 +3706,19 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="T7">
-        <v>20</v>
+        <v>15.2</v>
       </c>
       <c r="U7">
         <v>0</v>
       </c>
       <c r="V7">
-        <v>45</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3756,16 +3774,16 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S8">
         <v>100</v>
       </c>
       <c r="T8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="U8">
-        <v>92.2</v>
+        <v>94.3</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3821,7 +3839,7 @@
         <v>87.5</v>
       </c>
       <c r="Q9">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -3830,13 +3848,13 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>84</v>
+        <v>95.5</v>
       </c>
       <c r="U9">
-        <v>90.2</v>
+        <v>94.3</v>
       </c>
       <c r="V9">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3898,10 +3916,10 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="U10">
-        <v>96.09999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -3966,10 +3984,10 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="U11">
-        <v>92.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4025,22 +4043,22 @@
         <v>67.5</v>
       </c>
       <c r="Q12">
-        <v>75</v>
+        <v>46.9</v>
       </c>
       <c r="R12">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="S12">
         <v>50</v>
       </c>
       <c r="T12">
-        <v>60</v>
+        <v>45.5</v>
       </c>
       <c r="U12">
-        <v>88.2</v>
+        <v>92</v>
       </c>
       <c r="V12">
-        <v>50</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4093,7 +4111,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4102,10 +4120,10 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="U13">
-        <v>90.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4170,10 +4188,10 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>98</v>
+        <v>98.5</v>
       </c>
       <c r="U14">
-        <v>96.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4238,10 +4256,10 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="U15">
-        <v>94.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -4297,22 +4315,22 @@
         <v>87.5</v>
       </c>
       <c r="Q16">
-        <v>70</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="R16">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U16">
-        <v>88.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="V16">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4365,7 +4383,7 @@
         <v>82.5</v>
       </c>
       <c r="Q17">
-        <v>77.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4374,10 +4392,10 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>86</v>
+        <v>95.5</v>
       </c>
       <c r="U17">
-        <v>88.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4433,19 +4451,19 @@
         <v>85</v>
       </c>
       <c r="Q18">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R18">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="S18">
         <v>100</v>
       </c>
       <c r="T18">
-        <v>76</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U18">
-        <v>90.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -4501,22 +4519,22 @@
         <v>75</v>
       </c>
       <c r="Q19">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="R19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S19">
         <v>31.3</v>
       </c>
       <c r="T19">
-        <v>76</v>
+        <v>72.7</v>
       </c>
       <c r="U19">
-        <v>92.2</v>
+        <v>94.3</v>
       </c>
       <c r="V19">
-        <v>81.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4572,19 +4590,19 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>84</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="U20">
-        <v>92.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V20">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4649,7 +4667,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>96.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4714,10 +4732,10 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="U22">
-        <v>92.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4773,22 +4791,22 @@
         <v>92.5</v>
       </c>
       <c r="Q23">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R23">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S23">
         <v>100</v>
       </c>
       <c r="T23">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="U23">
-        <v>92.2</v>
+        <v>94.3</v>
       </c>
       <c r="V23">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4850,10 +4868,10 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U24">
-        <v>90.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -4918,10 +4936,10 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="U25">
-        <v>90.2</v>
+        <v>94.3</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -4986,13 +5004,13 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>78</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="U26">
-        <v>90.2</v>
+        <v>94.3</v>
       </c>
       <c r="V26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5054,10 +5072,10 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>98</v>
+        <v>98.5</v>
       </c>
       <c r="U27">
-        <v>96.09999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5122,10 +5140,10 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="U28">
-        <v>96.09999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5190,10 +5208,10 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="U29">
-        <v>92.2</v>
+        <v>94.3</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5249,22 +5267,22 @@
         <v>90</v>
       </c>
       <c r="Q30">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="R30">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S30">
         <v>100</v>
       </c>
       <c r="T30">
-        <v>48</v>
+        <v>51.5</v>
       </c>
       <c r="U30">
-        <v>86.3</v>
+        <v>90.8</v>
       </c>
       <c r="V30">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5326,10 +5344,10 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>88</v>
+        <v>95.5</v>
       </c>
       <c r="U31">
-        <v>94.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -5358,10 +5376,10 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>92</v>
+        <v>98.5</v>
       </c>
       <c r="U32">
-        <v>92.2</v>
+        <v>94.3</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -5421,28 +5439,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>58.6</v>
+        <v>64.3</v>
       </c>
       <c r="G2" s="2">
-        <v>41.4</v>
+        <v>35.7</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5453,7 +5471,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5462,19 +5480,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>60.7</v>
+        <v>75</v>
       </c>
       <c r="G3" s="2">
-        <v>39.3</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5485,28 +5503,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>64.3</v>
+        <v>82.8</v>
       </c>
       <c r="G4" s="2">
-        <v>35.7</v>
+        <v>17.2</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5517,7 +5535,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5526,19 +5544,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>75</v>
+        <v>85.7</v>
       </c>
       <c r="G5" s="2">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5549,7 +5567,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5558,19 +5576,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>14.3</v>
+        <v>7.1</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5590,19 +5608,19 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>86.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>13.8</v>
+        <v>6.9</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5613,7 +5631,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
@@ -5622,19 +5640,19 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>86.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>13.8</v>
+        <v>3.4</v>
       </c>
       <c r="H8">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5684,7 +5702,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5716,22 +5734,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920189</v>
+        <v>21330051920386</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5739,19 +5757,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920189</v>
+        <v>21330051920386</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>55</v>
@@ -5762,22 +5780,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920209</v>
+        <v>21330051920199</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5785,22 +5803,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920209</v>
+        <v>21330051920199</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5808,22 +5826,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920186</v>
+        <v>21330051920201</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5831,22 +5849,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920187</v>
+        <v>21330051920201</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5854,19 +5872,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920190</v>
+        <v>21330051920203</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>54</v>
@@ -5877,22 +5895,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920192</v>
+        <v>21330051920203</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
         <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5900,24 +5918,139 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920207</v>
+        <v>21330051920213</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
         <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>54</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920213</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920187</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920189</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330061430023</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920209</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BEM - Estadisticos 20222.xlsx
+++ b/grupos/4BEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="80">
   <si>
     <t>Materia</t>
   </si>
@@ -185,15 +185,15 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
@@ -215,31 +215,28 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>LORENZO</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
   </si>
   <si>
     <t>LOPEZ</t>
@@ -248,52 +245,19 @@
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
   </si>
   <si>
     <t>GREGORIO</t>
   </si>
   <si>
     <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAIR</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
   </si>
 </sst>
 </file>
@@ -841,7 +805,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>9</v>
@@ -850,7 +814,7 @@
         <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -930,7 +894,7 @@
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>8</v>
@@ -939,7 +903,7 @@
         <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -960,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -1019,7 +983,7 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1028,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1040,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1049,7 +1013,7 @@
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1108,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -1117,7 +1081,7 @@
         <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -1197,7 +1161,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -1206,7 +1170,7 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1218,7 +1182,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1286,7 +1250,7 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -1295,7 +1259,7 @@
         <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1307,7 +1271,7 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1316,7 +1280,7 @@
         <v>6</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA9">
         <v>8</v>
@@ -1375,7 +1339,7 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1384,7 +1348,7 @@
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1405,7 +1369,7 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>9</v>
@@ -1464,7 +1428,7 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -1473,7 +1437,7 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1553,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>5</v>
@@ -1562,7 +1526,7 @@
         <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -1642,7 +1606,7 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>8</v>
@@ -1651,7 +1615,7 @@
         <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1731,7 +1695,7 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1740,7 +1704,7 @@
         <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1761,7 +1725,7 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1820,7 +1784,7 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -1829,7 +1793,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1850,7 +1814,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -1909,7 +1873,7 @@
         <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>5</v>
@@ -1918,7 +1882,7 @@
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -1939,7 +1903,7 @@
         <v>6</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>7</v>
@@ -1998,7 +1962,7 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -2007,7 +1971,7 @@
         <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>4</v>
@@ -2028,7 +1992,7 @@
         <v>6</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>6</v>
@@ -2087,7 +2051,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>8</v>
@@ -2096,7 +2060,7 @@
         <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2108,7 +2072,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2117,7 +2081,7 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2176,7 +2140,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>6</v>
@@ -2185,7 +2149,7 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>4</v>
@@ -2265,7 +2229,7 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>9</v>
@@ -2274,7 +2238,7 @@
         <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -2295,7 +2259,7 @@
         <v>6</v>
       </c>
       <c r="Z20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA20">
         <v>5</v>
@@ -2354,7 +2318,7 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -2363,7 +2327,7 @@
         <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2443,7 +2407,7 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -2452,7 +2416,7 @@
         <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>6</v>
@@ -2473,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>7</v>
@@ -2532,7 +2496,7 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>9</v>
@@ -2541,7 +2505,7 @@
         <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2562,7 +2526,7 @@
         <v>6</v>
       </c>
       <c r="Z23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -2621,7 +2585,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2630,7 +2594,7 @@
         <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2651,7 +2615,7 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA24">
         <v>10</v>
@@ -2710,7 +2674,7 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2719,7 +2683,7 @@
         <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>8</v>
@@ -2799,7 +2763,7 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>9</v>
@@ -2808,7 +2772,7 @@
         <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>6</v>
@@ -2820,7 +2784,7 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2888,7 +2852,7 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
         <v>10</v>
@@ -2897,7 +2861,7 @@
         <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2909,7 +2873,7 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2977,7 +2941,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2986,7 +2950,7 @@
         <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -3066,7 +3030,7 @@
         <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>8</v>
@@ -3075,7 +3039,7 @@
         <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>4</v>
@@ -3155,7 +3119,7 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>7</v>
@@ -3164,7 +3128,7 @@
         <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>3</v>
@@ -3185,7 +3149,7 @@
         <v>6</v>
       </c>
       <c r="Z30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA30">
         <v>5</v>
@@ -3244,7 +3208,7 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
         <v>6</v>
@@ -3253,7 +3217,7 @@
         <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3274,7 +3238,7 @@
         <v>9</v>
       </c>
       <c r="Z31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA31">
         <v>9</v>
@@ -3564,7 +3528,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3700,7 +3664,7 @@
         <v>45</v>
       </c>
       <c r="P7">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -3768,7 +3732,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3836,7 +3800,7 @@
         <v>95</v>
       </c>
       <c r="P9">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q9">
         <v>90.59999999999999</v>
@@ -3904,7 +3868,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4040,7 +4004,7 @@
         <v>50</v>
       </c>
       <c r="P12">
-        <v>67.5</v>
+        <v>42.2</v>
       </c>
       <c r="Q12">
         <v>46.9</v>
@@ -4049,7 +4013,7 @@
         <v>31.3</v>
       </c>
       <c r="S12">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T12">
         <v>45.5</v>
@@ -4108,7 +4072,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q13">
         <v>93.8</v>
@@ -4176,7 +4140,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4244,7 +4208,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4380,7 +4344,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q17">
         <v>85.90000000000001</v>
@@ -4448,7 +4412,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q18">
         <v>90.59999999999999</v>
@@ -4516,7 +4480,7 @@
         <v>81.7</v>
       </c>
       <c r="P19">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q19">
         <v>81.3</v>
@@ -4525,7 +4489,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S19">
-        <v>31.3</v>
+        <v>54.2</v>
       </c>
       <c r="T19">
         <v>72.7</v>
@@ -4720,7 +4684,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4788,7 +4752,7 @@
         <v>91.7</v>
       </c>
       <c r="P23">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q23">
         <v>84.40000000000001</v>
@@ -4992,7 +4956,7 @@
         <v>90</v>
       </c>
       <c r="P26">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5060,7 +5024,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5196,7 +5160,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5264,7 +5228,7 @@
         <v>96.7</v>
       </c>
       <c r="P30">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q30">
         <v>87.5</v>
@@ -5332,7 +5296,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5448,19 +5412,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>64.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>35.7</v>
+        <v>21.4</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5471,28 +5435,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>75</v>
+        <v>82.8</v>
       </c>
       <c r="G3" s="2">
-        <v>25</v>
+        <v>17.2</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5503,28 +5467,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>24</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>82.8</v>
+        <v>85.7</v>
       </c>
       <c r="G4" s="2">
-        <v>17.2</v>
+        <v>14.3</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5535,7 +5499,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5556,7 +5520,7 @@
         <v>14.3</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5702,7 +5666,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5734,22 +5698,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920386</v>
+        <v>21330051920203</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5757,19 +5721,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920386</v>
+        <v>21330051920203</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>55</v>
@@ -5780,16 +5744,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920199</v>
+        <v>21330051920213</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5803,19 +5767,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920199</v>
+        <v>21330051920213</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>55</v>
@@ -5826,22 +5790,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920201</v>
+        <v>19330061430023</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5849,22 +5813,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920201</v>
+        <v>21330051920386</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5872,16 +5836,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920203</v>
+        <v>21330051920199</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5890,167 +5854,6 @@
         <v>54</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920203</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920213</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920213</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920187</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920189</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330061430023</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920209</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>
